--- a/data/out/variants/v9_date_range_all_lags/raw_v9_date_range_all_lags.xlsx
+++ b/data/out/variants/v9_date_range_all_lags/raw_v9_date_range_all_lags.xlsx
@@ -526,19 +526,19 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.3169084704573812</v>
+        <v>0.3169084704573838</v>
       </c>
       <c r="G2" t="n">
-        <v>33.49804106953745</v>
+        <v>33.49804106953713</v>
       </c>
       <c r="H2" t="n">
-        <v>6589.623820890948</v>
+        <v>6589.623820890924</v>
       </c>
       <c r="I2" t="n">
-        <v>81.17649795902105</v>
+        <v>81.17649795902091</v>
       </c>
       <c r="J2" t="n">
-        <v>20.68061951966757</v>
+        <v>20.68061951966735</v>
       </c>
       <c r="K2" t="n">
         <v>13081</v>
@@ -550,7 +550,7 @@
         <v>2617</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05091285705566406</v>
+        <v>0.04337692260742188</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -580,19 +580,19 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.3173141247061417</v>
+        <v>0.3172996571899531</v>
       </c>
       <c r="G3" t="n">
-        <v>33.50477934030788</v>
+        <v>33.50701953339612</v>
       </c>
       <c r="H3" t="n">
-        <v>6585.710569466988</v>
+        <v>6585.850134203459</v>
       </c>
       <c r="I3" t="n">
-        <v>81.15239102741822</v>
+        <v>81.15325091580409</v>
       </c>
       <c r="J3" t="n">
-        <v>20.69258845412333</v>
+        <v>20.69492504442389</v>
       </c>
       <c r="K3" t="n">
         <v>13081</v>
@@ -604,7 +604,7 @@
         <v>2617</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0391695499420166</v>
+        <v>0.02720260620117188</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -634,19 +634,19 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.3549224705520555</v>
+        <v>0.3541540546216552</v>
       </c>
       <c r="G4" t="n">
-        <v>25.72950671465416</v>
+        <v>25.85441233422993</v>
       </c>
       <c r="H4" t="n">
-        <v>6222.911675127783</v>
+        <v>6230.32440343772</v>
       </c>
       <c r="I4" t="n">
-        <v>78.88543385903245</v>
+        <v>78.93240401405319</v>
       </c>
       <c r="J4" t="n">
-        <v>13.91601610222986</v>
+        <v>14.01893362313515</v>
       </c>
       <c r="K4" t="n">
         <v>13081</v>
@@ -658,7 +658,7 @@
         <v>2617</v>
       </c>
       <c r="N4" t="n">
-        <v>2.109846830368042</v>
+        <v>1.798996210098267</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3174079061605241</v>
+        <v>0.3173848308968688</v>
       </c>
       <c r="G5" t="n">
-        <v>33.49517815050996</v>
+        <v>33.49876685995432</v>
       </c>
       <c r="H5" t="n">
-        <v>6584.805881765518</v>
+        <v>6585.02848342354</v>
       </c>
       <c r="I5" t="n">
-        <v>81.14681683076373</v>
+        <v>81.14818841738575</v>
       </c>
       <c r="J5" t="n">
-        <v>20.68596670802134</v>
+        <v>20.68969543248189</v>
       </c>
       <c r="K5" t="n">
         <v>13081</v>
@@ -716,7 +716,7 @@
         <v>2617</v>
       </c>
       <c r="N5" t="n">
-        <v>18.21357131004333</v>
+        <v>16.57859230041504</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-119.5598829715364</v>
+        <v>-119.5591815545083</v>
       </c>
     </row>
     <row r="6">
@@ -748,23 +748,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'min_samples_split': 10}</t>
+          <t>{'max_depth': 5, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.0143420297293354</v>
+        <v>0.01434202972933518</v>
       </c>
       <c r="G6" t="n">
-        <v>67.59830700806998</v>
+        <v>67.59830700807001</v>
       </c>
       <c r="H6" t="n">
-        <v>9508.411331780915</v>
+        <v>9508.411331780917</v>
       </c>
       <c r="I6" t="n">
         <v>97.51108312279644</v>
       </c>
       <c r="J6" t="n">
-        <v>52.4788485895123</v>
+        <v>52.47884858951232</v>
       </c>
       <c r="K6" t="n">
         <v>13081</v>
@@ -776,7 +776,7 @@
         <v>2617</v>
       </c>
       <c r="N6" t="n">
-        <v>4.64973783493042</v>
+        <v>3.436632633209229</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-226.4746248621064</v>
+        <v>-226.4924570535168</v>
       </c>
     </row>
     <row r="7">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1391544060609342</v>
+        <v>0.1397371239259205</v>
       </c>
       <c r="G7" t="n">
-        <v>62.75846529286101</v>
+        <v>62.74980664047574</v>
       </c>
       <c r="H7" t="n">
-        <v>8304.375602092667</v>
+        <v>8298.754259479116</v>
       </c>
       <c r="I7" t="n">
-        <v>91.12834686360038</v>
+        <v>91.09749864556719</v>
       </c>
       <c r="J7" t="n">
-        <v>48.28153456666307</v>
+        <v>48.27509707991042</v>
       </c>
       <c r="K7" t="n">
         <v>13081</v>
@@ -836,7 +836,7 @@
         <v>2617</v>
       </c>
       <c r="N7" t="n">
-        <v>933.7538921833038</v>
+        <v>900.406103849411</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-213.9219679100253</v>
+        <v>-213.9810360884843</v>
       </c>
     </row>
     <row r="8">
@@ -868,23 +868,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.01, 'max_depth': 3, 'n_estimators': 500}</t>
+          <t>{'learning_rate': 0.05, 'max_depth': 3, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.4529099128172575</v>
+        <v>0.4495819628624542</v>
       </c>
       <c r="G8" t="n">
-        <v>40.66997930622452</v>
+        <v>40.55588681682178</v>
       </c>
       <c r="H8" t="n">
-        <v>5277.649794730443</v>
+        <v>5309.753747639343</v>
       </c>
       <c r="I8" t="n">
-        <v>72.64743488059605</v>
+        <v>72.86805711448153</v>
       </c>
       <c r="J8" t="n">
-        <v>28.79621493918762</v>
+        <v>28.5944287602898</v>
       </c>
       <c r="K8" t="n">
         <v>13081</v>
@@ -896,7 +896,7 @@
         <v>2617</v>
       </c>
       <c r="N8" t="n">
-        <v>464.413991689682</v>
+        <v>408.5224452018738</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-226.6203664551349</v>
+        <v>-225.7838233956215</v>
       </c>
     </row>
     <row r="9">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-5.556077835208853</v>
+        <v>-5.403412281827443</v>
       </c>
       <c r="G9" t="n">
-        <v>232.6747291961471</v>
+        <v>229.669227279906</v>
       </c>
       <c r="H9" t="n">
-        <v>63244.94567138678</v>
+        <v>61772.21687343896</v>
       </c>
       <c r="I9" t="n">
-        <v>251.4854780526836</v>
+        <v>248.5401715486632</v>
       </c>
       <c r="J9" t="n">
-        <v>199.5052786548177</v>
+        <v>197.074060043372</v>
       </c>
       <c r="K9" t="n">
         <v>13081</v>
@@ -956,7 +956,7 @@
         <v>2617</v>
       </c>
       <c r="N9" t="n">
-        <v>41.69150829315186</v>
+        <v>29.60560607910156</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-470.5934539280529</v>
+        <v>-468.8604984411263</v>
       </c>
     </row>
     <row r="10">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-1.152573421436736</v>
+        <v>-1.189886807625314</v>
       </c>
       <c r="G10" t="n">
-        <v>114.7333528031006</v>
+        <v>115.7287695834926</v>
       </c>
       <c r="H10" t="n">
-        <v>20765.37108228225</v>
+        <v>21125.32456996639</v>
       </c>
       <c r="I10" t="n">
-        <v>144.1019468372383</v>
+        <v>145.3455350878258</v>
       </c>
       <c r="J10" t="n">
-        <v>93.97117966587794</v>
+        <v>94.95445443354737</v>
       </c>
       <c r="K10" t="n">
         <v>13081</v>
@@ -1016,7 +1016,7 @@
         <v>2617</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6579675674438477</v>
+        <v>0.748507022857666</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-315.830391058111</v>
+        <v>-317.9533986376432</v>
       </c>
     </row>
     <row r="11">
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 458, 'learning_rate': 0.01775389983622478, 'max_depth': 3, 'subsample': 0.7993165483576385, 'colsample_bytree': 0.6882202621515524}</t>
+          <t>{'n_estimators': 379, 'learning_rate': 0.014192525942229913, 'max_depth': 3, 'subsample': 0.7319953250384384, 'colsample_bytree': 0.9997762125379739}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.4883821628835361</v>
+        <v>0.4431910405285141</v>
       </c>
       <c r="G11" t="n">
-        <v>33.13065226477979</v>
+        <v>39.73015338797126</v>
       </c>
       <c r="H11" t="n">
-        <v>4935.457315526576</v>
+        <v>5371.405476914033</v>
       </c>
       <c r="I11" t="n">
-        <v>70.2528100187215</v>
+        <v>73.28987294922835</v>
       </c>
       <c r="J11" t="n">
-        <v>21.85547249215544</v>
+        <v>27.99911483660165</v>
       </c>
       <c r="K11" t="n">
         <v>13081</v>
@@ -1076,7 +1076,7 @@
         <v>2617</v>
       </c>
       <c r="N11" t="n">
-        <v>105.8745801448822</v>
+        <v>104.9304258823395</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 531, 'learning_rate': 0.010051436841474751, 'num_leaves': 58, 'min_child_samples': 16}</t>
+          <t>{'n_estimators': 323, 'learning_rate': 0.0249500583748754, 'num_leaves': 46, 'min_child_samples': 21}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.4378064415882138</v>
+        <v>0.51233717210643</v>
       </c>
       <c r="G12" t="n">
-        <v>49.4491589996305</v>
+        <v>40.00009710564376</v>
       </c>
       <c r="H12" t="n">
-        <v>5423.349440363126</v>
+        <v>4704.368958289091</v>
       </c>
       <c r="I12" t="n">
-        <v>73.64339373197792</v>
+        <v>68.58840250573775</v>
       </c>
       <c r="J12" t="n">
-        <v>37.3917763317256</v>
+        <v>28.82074135187185</v>
       </c>
       <c r="K12" t="n">
         <v>13081</v>
@@ -1134,7 +1134,7 @@
         <v>2617</v>
       </c>
       <c r="N12" t="n">
-        <v>388.5727872848511</v>
+        <v>311.1738862991333</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 731, 'learning_rate': 0.031207054462903394, 'depth': 4}</t>
+          <t>{'iterations': 609, 'learning_rate': 0.016025123904735487, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.4470366883504042</v>
+        <v>0.4562936475237567</v>
       </c>
       <c r="G13" t="n">
-        <v>39.77905037549748</v>
+        <v>37.4701544925933</v>
       </c>
       <c r="H13" t="n">
-        <v>5334.307414066067</v>
+        <v>5245.007699401794</v>
       </c>
       <c r="I13" t="n">
-        <v>73.03634310441663</v>
+        <v>72.42242539021869</v>
       </c>
       <c r="J13" t="n">
-        <v>28.4669416941996</v>
+        <v>25.74544197142637</v>
       </c>
       <c r="K13" t="n">
         <v>13081</v>
@@ -1192,7 +1192,7 @@
         <v>2617</v>
       </c>
       <c r="N13" t="n">
-        <v>407.9295263290405</v>
+        <v>337.9638175964355</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.4457543657400969</v>
+        <v>0.3638164440950643</v>
       </c>
       <c r="G14" t="n">
-        <v>44.1614216687634</v>
+        <v>55.32244391797226</v>
       </c>
       <c r="H14" t="n">
-        <v>5346.677679621265</v>
+        <v>6137.113597730122</v>
       </c>
       <c r="I14" t="n">
-        <v>73.12097975014602</v>
+        <v>78.3397319227614</v>
       </c>
       <c r="J14" t="n">
-        <v>32.15888233209694</v>
+        <v>42.16659078955041</v>
       </c>
       <c r="K14" t="n">
         <v>13081</v>
@@ -1250,7 +1250,7 @@
         <v>2617</v>
       </c>
       <c r="N14" t="n">
-        <v>152.980259180069</v>
+        <v>152.7698662281036</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-218.3767300947517</v>
+        <v>-222.2601423041553</v>
       </c>
     </row>
     <row r="15">
@@ -1310,7 +1310,7 @@
         <v>2617</v>
       </c>
       <c r="N15" t="n">
-        <v>43.75834727287292</v>
+        <v>32.53524279594421</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1342,23 +1342,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.4038980640825263</v>
+        <v>0.4070354692272449</v>
       </c>
       <c r="G16" t="n">
-        <v>28.71585787877257</v>
+        <v>28.64668987352446</v>
       </c>
       <c r="H16" t="n">
-        <v>5750.45560765648</v>
+        <v>5720.189795853388</v>
       </c>
       <c r="I16" t="n">
-        <v>75.83175856892994</v>
+        <v>75.63193634869722</v>
       </c>
       <c r="J16" t="n">
-        <v>16.70276958049577</v>
+        <v>16.64980419193196</v>
       </c>
       <c r="K16" t="n">
         <v>13081</v>
@@ -1370,7 +1370,7 @@
         <v>2617</v>
       </c>
       <c r="N16" t="n">
-        <v>497.8099279403687</v>
+        <v>473.7408821582794</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-139.9302501037841</v>
+        <v>-137.95031073271</v>
       </c>
     </row>
   </sheetData>
